--- a/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos crónicos de la piel</t>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,98</t>
+          <t>1,39; 11,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,72</t>
+          <t>1,01; 7,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,62</t>
+          <t>0,52; 4,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,31</t>
+          <t>1,57; 7,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,18</t>
+          <t>1,23; 6,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,75</t>
+          <t>1,08; 7,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,44 +882,44 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,74</t>
+          <t>1,19; 6,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,63</t>
+          <t>1,17; 7,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,55</t>
+          <t>0,31; 2,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,74</t>
+          <t>0,3; 3,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,56</t>
+          <t>1,82; 6,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,35</t>
+          <t>1,79; 5,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 15,0</t>
+          <t>4,02; 15,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,97</t>
+          <t>0,86; 7,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,03</t>
+          <t>1,79; 10,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,11</t>
+          <t>2,21; 8,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,19</t>
+          <t>1,63; 7,48</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,44</t>
+          <t>1,31; 14,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,7</t>
+          <t>0,82; 7,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,05</t>
+          <t>0,49; 5,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,93</t>
+          <t>0,76; 5,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,32</t>
+          <t>0,56; 6,61</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 10,28</t>
+          <t>1,05; 10,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,21</t>
+          <t>0,87; 11,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,49</t>
+          <t>1,37; 7,59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,83</t>
+          <t>0,82; 9,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,91</t>
+          <t>1,34; 12,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,88</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,24</t>
+          <t>0,67; 8,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,11</t>
+          <t>1,93; 8,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,02</t>
+          <t>0,89; 6,16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,87</t>
+          <t>0,52; 5,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,89</t>
+          <t>3,17; 11,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,34</t>
+          <t>3,35; 10,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,86</t>
+          <t>0,5; 2,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,55</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,61</t>
+          <t>4,16; 9,42</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,6</t>
+          <t>0,4; 3,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,23</t>
+          <t>0,27; 3,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,94</t>
+          <t>0,49; 4,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,16</t>
+          <t>0,29; 3,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,82</t>
+          <t>0,73; 5,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,61</t>
+          <t>0,55; 4,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,6</t>
+          <t>0,44; 2,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,64</t>
+          <t>0,18; 1,65</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,35</t>
+          <t>0,74; 3,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,64</t>
+          <t>0,84; 3,93</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,68</t>
+          <t>1,73; 3,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,18</t>
+          <t>0,78; 2,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,85</t>
+          <t>2,35; 4,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,55</t>
+          <t>0,45; 1,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,23</t>
+          <t>0,79; 2,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,79</t>
+          <t>0,97; 2,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,53</t>
+          <t>2,29; 4,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,29</t>
+          <t>0,5; 1,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,61</t>
+          <t>1,4; 2,65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,12</t>
+          <t>1,06; 2,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,21</t>
+          <t>2,54; 4,19</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4371</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2913</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>735; 5964</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2067</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4883</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>615; 4764</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3744</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3066</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>585; 5529</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1789; 8803</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3753</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4832</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4482</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2249</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8854</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3672</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1278; 7244</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1374; 9682</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4093</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1310; 7492</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1497; 9919</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>657; 5396</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>643; 6776</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3895; 13035</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4553; 15125</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1632</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6489</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2742; 10245</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>499; 4389</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4527</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1205; 6886</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3066; 12031</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3823</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2040; 9377</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3456</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6414</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3545</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>919; 9909</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2442</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5040</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>667; 6466</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3535</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>784; 8493</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1201; 8362</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>832; 9794</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1484</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2767</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3209</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3764</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3628</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>363; 3577</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3877</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>355; 4627</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5081</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3732</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1028; 5712</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3600</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>459; 5446</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4323</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3106</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>804; 7372</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4178</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>374; 4903</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4458</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2244; 10450</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3381</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>912; 6300</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10348</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>18048</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4568</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>719; 7513</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5126</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3953; 14290</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3249</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3930</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5228; 16494</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4800</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1433; 7634</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>651; 6203</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>11678; 26430</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2583</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2765</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5590</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>629; 5308</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3422</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>451; 5238</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>647; 6054</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>481; 5518</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4174</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1247; 8890</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>855; 7434</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1409; 8370</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>594; 5543</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2467; 10647</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2424; 11338</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18278</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>9273</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>24771</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>28751</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>47102</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10293</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>12212; 26476</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5460; 15438</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>15613; 32889</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3276; 12282</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5933; 17055</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7258; 19103</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17429; 34768</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>6964; 18898</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>20404; 38533</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>15338; 30510</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>36197; 59866</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,26</t>
+          <t>1,31; 12,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,84</t>
+          <t>1,04; 9,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,9</t>
+          <t>0,52; 4,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,74</t>
+          <t>1,71; 8,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,97</t>
+          <t>1,2; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,63</t>
+          <t>1,12; 8,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,79</t>
+          <t>1,2; 6,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,77</t>
+          <t>1,13; 7,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,14</t>
+          <t>0,3; 3,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,08</t>
+          <t>1,77; 6,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,94</t>
+          <t>1,55; 6,13</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,03</t>
+          <t>3,98; 16,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,53</t>
+          <t>0,85; 8,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,25</t>
+          <t>1,87; 10,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,67</t>
+          <t>2,4; 8,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,48</t>
+          <t>1,97; 8,04</t>
         </is>
       </c>
     </row>
@@ -1142,32 +1142,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,25</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,13</t>
+          <t>1,31; 11,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,96</t>
+          <t>0,82; 7,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,31</t>
+          <t>0,5; 5,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,29</t>
+          <t>0,76; 4,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,61</t>
+          <t>0,58; 6,14</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 8,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 8,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,37</t>
+          <t>1,09; 11,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,36</t>
+          <t>0,85; 9,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,59</t>
+          <t>1,51; 7,53</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,73</t>
+          <t>0,82; 10,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,24</t>
+          <t>1,28; 13,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,73</t>
+          <t>0,65; 8,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,99</t>
+          <t>1,87; 8,07</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,16</t>
+          <t>0,98; 6,61</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,42</t>
+          <t>0,94; 5,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 11,48</t>
+          <t>3,17; 10,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,57</t>
+          <t>3,6; 11,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,68</t>
+          <t>0,49; 2,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,2</t>
+          <t>0,25; 2,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,42</t>
+          <t>4,15; 9,5</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1697,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,36</t>
+          <t>0,4; 3,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,19</t>
+          <t>0,28; 3,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,6</t>
+          <t>0,7; 5,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,36</t>
+          <t>0,29; 3,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,2</t>
+          <t>0,73; 4,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,74</t>
+          <t>0,54; 4,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,6</t>
+          <t>0,45; 2,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,18</t>
+          <t>0,8; 3,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,93</t>
+          <t>0,82; 3,83</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,51</t>
+          <t>0,38; 1,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,75</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,19</t>
+          <t>0,76; 2,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,94</t>
+          <t>2,22; 4,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,7</t>
+          <t>0,46; 1,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,28</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,56</t>
+          <t>1,03; 2,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,56</t>
+          <t>2,25; 4,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,35</t>
+          <t>0,52; 1,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,65</t>
+          <t>1,47; 2,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,11</t>
+          <t>1,09; 2,15</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,19</t>
+          <t>2,56; 4,18</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2913</t>
+          <t>0; 2950</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>735; 5964</t>
+          <t>695; 6812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>0; 2399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4883</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>615; 4764</t>
+          <t>629; 5803</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3744</t>
+          <t>0; 3770</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 3769</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>585; 5529</t>
+          <t>587; 5302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1789; 8803</t>
+          <t>1947; 9581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 3691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4832</t>
+          <t>0; 3419</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3672</t>
+          <t>0; 3299</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5756</t>
+          <t>0; 5047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1278; 7244</t>
+          <t>1250; 7527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1374; 9682</t>
+          <t>1419; 10232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 4685</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 3289</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1310; 7492</t>
+          <t>1324; 7459</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1497; 9919</t>
+          <t>1447; 9940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>657; 5396</t>
+          <t>657; 5412</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>643; 6776</t>
+          <t>647; 6582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3895; 13035</t>
+          <t>3783; 12947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4553; 15125</t>
+          <t>3942; 15605</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2742; 10245</t>
+          <t>2714; 11004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>499; 4389</t>
+          <t>494; 4716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4527</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3342</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1205; 6886</t>
+          <t>1253; 7103</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3066; 12031</t>
+          <t>3336; 12349</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 2718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2040; 9377</t>
+          <t>2470; 10081</t>
         </is>
       </c>
     </row>
@@ -2838,32 +2838,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6414</t>
+          <t>0; 5825</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 3695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>919; 9909</t>
+          <t>919; 8330</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2442</t>
+          <t>0; 3793</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 5986</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>667; 6466</t>
+          <t>666; 6029</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>0; 3627</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>784; 8493</t>
+          <t>805; 8730</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1201; 8362</t>
+          <t>1202; 7851</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>832; 9794</t>
+          <t>864; 9106</t>
         </is>
       </c>
     </row>
@@ -3041,22 +3041,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3209</t>
+          <t>0; 3269</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3764</t>
+          <t>0; 3533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 3731</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>363; 3577</t>
+          <t>376; 3814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3877</t>
+          <t>0; 3540</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>355; 4627</t>
+          <t>346; 3835</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 2586</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5081</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1028; 5712</t>
+          <t>1138; 5665</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 4294</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>459; 5446</t>
+          <t>462; 5681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,47 +3264,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4323</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3471</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>804; 7372</t>
+          <t>774; 8054</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 3475</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>374; 4903</t>
+          <t>366; 4754</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4054</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2244; 10450</t>
+          <t>2170; 9380</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 5376</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>912; 6300</t>
+          <t>999; 6769</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>719; 7513</t>
+          <t>1304; 6987</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5126</t>
+          <t>0; 4193</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3953; 14290</t>
+          <t>3943; 13072</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 4063</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3930</t>
+          <t>0; 4486</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5228; 16494</t>
+          <t>5620; 17597</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 5156</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1433; 7634</t>
+          <t>1388; 8299</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>651; 6203</t>
+          <t>700; 6404</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11678; 26430</t>
+          <t>11628; 26661</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>629; 5308</t>
+          <t>628; 5525</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3422</t>
+          <t>0; 3740</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>451; 5238</t>
+          <t>453; 5187</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>647; 6054</t>
+          <t>918; 7005</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>481; 5518</t>
+          <t>480; 5354</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>0; 3882</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1247; 8890</t>
+          <t>1242; 8180</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>855; 7434</t>
+          <t>853; 7297</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1409; 8370</t>
+          <t>1457; 8472</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>594; 5543</t>
+          <t>592; 5561</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2467; 10647</t>
+          <t>2691; 11180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2424; 11338</t>
+          <t>2354; 11058</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2517; 10293</t>
+          <t>2582; 10688</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12212; 26476</t>
+          <t>11700; 25770</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5460; 15438</t>
+          <t>5346; 15234</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15613; 32889</t>
+          <t>14743; 31410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3276; 12282</t>
+          <t>3307; 11581</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5933; 17055</t>
+          <t>5931; 16942</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7258; 19103</t>
+          <t>7657; 19954</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17429; 34768</t>
+          <t>17113; 34309</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6964; 18898</t>
+          <t>7264; 18556</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20404; 38533</t>
+          <t>21325; 40005</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15338; 30510</t>
+          <t>15728; 31162</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>36197; 59866</t>
+          <t>36581; 59673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,57%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,86</t>
+          <t>1,03; 8,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,75</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,64</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,97; 10,98</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,12</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,05</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 9,55</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,85</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,75</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,7</t>
+          <t>0,52; 4,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,42</t>
+          <t>1,63; 7,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,24</t>
+          <t>1,21; 6,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,07</t>
+          <t>1,13; 7,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,76</t>
+          <t>1,24; 7,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,79</t>
+          <t>1,72; 9,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,57</t>
+          <t>0,31; 2,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,05</t>
+          <t>0,3; 3,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,04</t>
+          <t>1,8; 5,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,13</t>
+          <t>2,07; 7,13</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>4,68%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1002,37 +1002,37 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 16,14</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,89</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2,08; 12,3</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 8,09</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,97; 15,0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,78</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,58</t>
+          <t>0,83; 7,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,9</t>
+          <t>2,16; 9,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,04</t>
+          <t>1,85; 7,09</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,13</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,81; 7,7</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 11,88</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,43</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,51; 14,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,46</t>
+          <t>0,65; 5,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,96</t>
+          <t>0,76; 4,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,14</t>
+          <t>0,74; 7,02</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,05</t>
+          <t>0,67; 9,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,42</t>
+          <t>0,85; 10,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,53</t>
+          <t>1,32; 7,38</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 10,15</t>
+          <t>1,31; 11,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,88</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,53; 8,02</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,36</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,83; 8,83</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,72</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,81</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 13,37</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,02</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,46</t>
+          <t>0,0; 9,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,07</t>
+          <t>1,84; 8,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,61</t>
+          <t>0,95; 6,05</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,04</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,5</t>
+          <t>4,17; 12,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,97; 5,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,28</t>
+          <t>3,38; 11,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,92</t>
+          <t>0,48; 2,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,28</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,5</t>
+          <t>4,64; 10,61</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,5</t>
+          <t>0,29; 3,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,16</t>
+          <t>0,73; 4,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,32</t>
+          <t>0,57; 4,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,26</t>
+          <t>0,4; 3,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,79</t>
+          <t>0,28; 3,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,65</t>
+          <t>0,58; 4,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,63</t>
+          <t>0,5; 2,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,65</t>
+          <t>0,18; 1,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,34</t>
+          <t>0,74; 3,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,83</t>
+          <t>0,82; 3,69</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,45; 1,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>0,78; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,16</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,72</t>
+          <t>2,35; 4,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,6</t>
+          <t>0,31; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,26</t>
+          <t>1,72; 3,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,68</t>
+          <t>0,75; 2,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,5</t>
+          <t>2,51; 5,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,32</t>
+          <t>0,52; 1,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,75</t>
+          <t>1,46; 2,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,15</t>
+          <t>1,09; 2,12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,18</t>
+          <t>2,66; 4,49</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,44 +2141,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2421</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1984</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>657</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2950</t>
+          <t>0; 4386</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>695; 6812</t>
+          <t>628; 5297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2399</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 3046</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2965</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>513; 5817</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2364</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4244</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>629; 5803</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3770</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3769</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>587; 5302</t>
+          <t>583; 5208</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1947; 9581</t>
+          <t>1858; 8312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3419</t>
+          <t>0; 3112</t>
         </is>
       </c>
     </row>
@@ -2281,37 +2281,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1595</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3739</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4482</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3388</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8489</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3299</t>
+          <t>0; 4085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5047</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1250; 7527</t>
+          <t>1332; 7438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1419; 10232</t>
+          <t>1303; 8646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4685</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3289</t>
+          <t>0; 5269</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1324; 7459</t>
+          <t>1287; 7465</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1447; 9940</t>
+          <t>1725; 10047</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>657; 5412</t>
+          <t>661; 5363</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>647; 6582</t>
+          <t>646; 8083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3783; 12947</t>
+          <t>3848; 11910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3942; 15605</t>
+          <t>4482; 15429</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2562,57 +2562,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>5744</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1632</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6489</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3372</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6489</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4608</t>
         </is>
       </c>
     </row>
@@ -2630,37 +2630,37 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2714; 11004</t>
+          <t>0; 3008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 2718</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1235; 7302</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>494; 4716</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2709; 10230</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3706</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3342</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1253; 7103</t>
+          <t>468; 4482</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3336; 12349</t>
+          <t>3004; 12636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2718</t>
+          <t>0; 3799</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2470; 10081</t>
+          <t>2145; 8216</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,49 +2765,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1814</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1153</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3456</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3374</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3750</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3023</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5862</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>660; 6252</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 5825</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3695</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>919; 8330</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3793</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5986</t>
+          <t>0; 6131</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>666; 6029</t>
+          <t>0; 4042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1072; 10292</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3627</t>
+          <t>0; 3040</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>805; 8730</t>
+          <t>1041; 8080</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1202; 7851</t>
+          <t>1199; 7800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>864; 9106</t>
+          <t>1055; 10037</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2634</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3269</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 3531</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>376; 3814</t>
+          <t>267; 3599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 3014</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2766</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>346; 3835</t>
+          <t>303; 3850</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2586</t>
+          <t>0; 2837</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 5068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 3351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1138; 5665</t>
+          <t>995; 5549</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,62 +3181,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2968</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1958</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>739</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1337</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2616</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>462; 5681</t>
+          <t>790; 7177</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0; 3973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>261; 3924</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3565</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>464; 4944</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3565</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3471</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>774; 8054</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3475</t>
-        </is>
-      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>366; 4754</t>
+          <t>0; 4332</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4054</t>
+          <t>0; 4697</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2170; 9380</t>
+          <t>2135; 9421</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5376</t>
+          <t>0; 3711</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>999; 6769</t>
+          <t>897; 5730</t>
         </is>
       </c>
     </row>
@@ -3326,37 +3326,37 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10688</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3404</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1316</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7700</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18048</t>
+          <t>18652</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 3264</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1304; 6987</t>
+          <t>0; 3147</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4193</t>
+          <t>0; 4568</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3943; 13072</t>
+          <t>5901; 18037</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3910</t>
+          <t>0; 2964</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4063</t>
+          <t>1341; 8142</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 4503</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5620; 17597</t>
+          <t>4138; 13919</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5156</t>
+          <t>0; 4210</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1388; 8299</t>
+          <t>1355; 8150</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>700; 6404</t>
+          <t>767; 7178</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11628; 26661</t>
+          <t>12249; 27989</t>
         </is>
       </c>
     </row>
@@ -3534,37 +3534,37 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>2046</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1934</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2583</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1277</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3656</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5561</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>628; 5525</t>
+          <t>476; 5192</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 4513</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>453; 5187</t>
+          <t>1245; 8235</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>918; 7005</t>
+          <t>914; 7596</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>480; 5354</t>
+          <t>628; 5692</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3882</t>
+          <t>0; 2964</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1242; 8180</t>
+          <t>453; 5302</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>853; 7297</t>
+          <t>812; 6926</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1457; 8472</t>
+          <t>1605; 8369</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>592; 5561</t>
+          <t>597; 5520</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2691; 11180</t>
+          <t>2483; 11236</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2354; 11058</t>
+          <t>2445; 11055</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2582; 10688</t>
+          <t>3225; 11189</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11700; 25770</t>
+          <t>5802; 16679</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5346; 15234</t>
+          <t>7671; 20758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14743; 31410</t>
+          <t>16439; 33216</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3307; 11581</t>
+          <t>2129; 10536</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5931; 16942</t>
+          <t>12126; 26014</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7657; 19954</t>
+          <t>5285; 15348</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17113; 34309</t>
+          <t>15793; 33047</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7264; 18556</t>
+          <t>7253; 18105</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21325; 40005</t>
+          <t>21301; 38030</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15728; 31162</t>
+          <t>15747; 30705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>36581; 59673</t>
+          <t>35412; 59721</t>
         </is>
       </c>
     </row>
